--- a/exams/INFORMATIQUE-JUSTICE-2025-E9.xlsx
+++ b/exams/INFORMATIQUE-JUSTICE-2025-E9.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="247">
   <si>
     <t>Question</t>
   </si>
@@ -1046,13 +1046,796 @@
   </si>
   <si>
     <t>Answer Option 6</t>
+  </si>
+  <si>
+    <t>Quel outil Linux permet d'afficher les interfaces réseau ?</t>
+  </si>
+  <si>
+    <t>ifconfig.</t>
+  </si>
+  <si>
+    <t>ps.</t>
+  </si>
+  <si>
+    <t>grep.</t>
+  </si>
+  <si>
+    <r>
+      <t>ifconfig</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> est l'outil classique pour configurer et afficher les interfaces. Bien qu'il soit remplacé par la commande </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>ip addr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> sur les distributions modernes, il reste la réponse correcte ici.</t>
+    </r>
+  </si>
+  <si>
+    <t>Quel est le rôle d'un NAT (Network Address Translation) ?</t>
+  </si>
+  <si>
+    <t>Convertir des adresses IP privées en IP publiques.</t>
+  </si>
+  <si>
+    <t>Gérer le DNS.</t>
+  </si>
+  <si>
+    <t>Attribuer des ports.</t>
+  </si>
+  <si>
+    <t>Le NAT permet d'économiser des adresses IPv4 publiques en permettant à un réseau entier (adresses privées RFC 1918) de sortir sur Internet via une seule adresse publique.</t>
+  </si>
+  <si>
+    <t>Que signifie le masque 255.255.255.192 ?</t>
+  </si>
+  <si>
+    <t>/30</t>
+  </si>
+  <si>
+    <t>/27</t>
+  </si>
+  <si>
+    <t>/28</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Le masque </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>255.255.255.192</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> correspond à un </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. En binaire, les trois premiers octets sont pleins (24 bits) et le dernier est </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>11000000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (2 bits), soit $24 + 2 = 26$.</t>
+    </r>
+  </si>
+  <si>
+    <t>Quel est le rôle principal d'un serveur proxy ?</t>
+  </si>
+  <si>
+    <t>Chiffrer les connexions VPN.</t>
+  </si>
+  <si>
+    <t>Stocker les fichiers partagés.</t>
+  </si>
+  <si>
+    <t>Intermédiaire entre l'utilisateur et Internet.</t>
+  </si>
+  <si>
+    <t>Un proxy agit comme un relais. Il peut servir à filtrer le contenu, cacher l'adresse IP interne de l'utilisateur ou mettre en cache des pages web pour accélérer l'accès.</t>
+  </si>
+  <si>
+    <t>À quoi sert la commande traceroute ?</t>
+  </si>
+  <si>
+    <t>Identifier les routeurs entre deux hôtes.</t>
+  </si>
+  <si>
+    <t>Scanner des ports.</t>
+  </si>
+  <si>
+    <t>Afficher l'adresse IP.</t>
+  </si>
+  <si>
+    <r>
+      <t>traceroute</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (ou </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>tracert</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> sous Windows) utilise le champ TTL de l'en-tête IP pour forcer chaque routeur sur le chemin à renvoyer un message d'erreur, révélant ainsi le saut (hop).</t>
+    </r>
+  </si>
+  <si>
+    <t>Quel protocole est utilisé pour établir une connexion VPN de type IPSec ?</t>
+  </si>
+  <si>
+    <t>HTTPS.</t>
+  </si>
+  <si>
+    <t>PPTP.</t>
+  </si>
+  <si>
+    <t>ESP.</t>
+  </si>
+  <si>
+    <r>
+      <t>ESP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Encapsulating Security Payload) assure le chiffrement et l'intégrité des données dans une architecture IPSec. L'autre protocole majeur associé est AH (Authentication Header).</t>
+    </r>
+  </si>
+  <si>
+    <t>Dans une trame Ethernet, quelle est la taille maximale des données utiles ?</t>
+  </si>
+  <si>
+    <t>512 octets.</t>
+  </si>
+  <si>
+    <t>1500 octets.</t>
+  </si>
+  <si>
+    <t>2048 octets.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">C'est ce qu'on appelle la </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MTU</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Maximum Transmission Unit) standard. Si les données dépassent 1500 octets, la trame est fragmentée (sauf si les "Jumbo Frames" sont activées).</t>
+    </r>
+  </si>
+  <si>
+    <t>Le protocole OSPF est un protocole de :</t>
+  </si>
+  <si>
+    <t>Routage à vecteur de distance.</t>
+  </si>
+  <si>
+    <t>Routage à état de lien.</t>
+  </si>
+  <si>
+    <t>Gestion des sessions.</t>
+  </si>
+  <si>
+    <r>
+      <t>OSPF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Open Shortest Path First) utilise l'algorithme de Dijkstra pour construire une carte complète de la topologie (Link State), contrairement au RIP qui ne voit que le nombre de sauts.</t>
+    </r>
+  </si>
+  <si>
+    <t>Quel protocole permet de découvrir automatiquement les équipements voisins ?</t>
+  </si>
+  <si>
+    <t>LLDP.</t>
+  </si>
+  <si>
+    <t>STP.</t>
+  </si>
+  <si>
+    <t>BGP.</t>
+  </si>
+  <si>
+    <r>
+      <t>LLDP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Link Layer Discovery Protocol) est un protocole standard (IEEE 802.1AB) qui permet aux équipements réseau de partager leur identité et leurs capacités avec leurs voisins directs.</t>
+    </r>
+  </si>
+  <si>
+    <t>Quel est le rôle du protocole STP (Spanning Tree Protocol) ?</t>
+  </si>
+  <si>
+    <t>Fournir du routage dynamique.</t>
+  </si>
+  <si>
+    <t>Éviter les boucles de commutation.</t>
+  </si>
+  <si>
+    <t>Gérer les VLANs.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Le </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>STP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (802.1D) détecte les chemins redondants dans un réseau commuté et bloque certains ports pour éviter les tempêtes de broadcast qui pourraient paralyser le réseau.</t>
+    </r>
+  </si>
+  <si>
+    <t>Quelle technologie permet d'inspecter le trafic réseau en profondeur jusqu'à la couche 7 ?</t>
+  </si>
+  <si>
+    <t>Switch niveau 2.</t>
+  </si>
+  <si>
+    <t>IDS classique.</t>
+  </si>
+  <si>
+    <t>Firewall applicatif (WAF ou NGFW).</t>
+  </si>
+  <si>
+    <r>
+      <t>Les firewalls de nouvelle génération (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>NGFW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) font du </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>DPI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Deep Packet Inspection), leur permettant de bloquer des applications spécifiques (ex: Facebook) même si le port est ouvert.</t>
+    </r>
+  </si>
+  <si>
+    <t>Quel protocole VPN est reconnu pour être rapide, moderne et basé sur UDP ?</t>
+  </si>
+  <si>
+    <t>L2TP/IPSec.</t>
+  </si>
+  <si>
+    <t>WireGuard.</t>
+  </si>
+  <si>
+    <r>
+      <t>WireGuard</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> est une solution moderne utilisant une cryptographie de pointe. Il est beaucoup plus performant et léger en code que IPsec ou OpenVPN.</t>
+    </r>
+  </si>
+  <si>
+    <t>IPsec peut fonctionner en deux modes : lequel cache l'adresse IP source et destination réelle ?</t>
+  </si>
+  <si>
+    <t>Tunnel mode.</t>
+  </si>
+  <si>
+    <t>NAT mode.</t>
+  </si>
+  <si>
+    <t>Encryption-only mode.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">En </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mode Tunnel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, le paquet IP original est entièrement chiffré et encapsulé dans un nouveau paquet IP. Les adresses source/destination réelles sont donc masquées par celles des passerelles VPN.</t>
+    </r>
+  </si>
+  <si>
+    <t>Quel protocole permet la résolution d'adresse MAC à partir d'une IP ?</t>
+  </si>
+  <si>
+    <t>DNS.</t>
+  </si>
+  <si>
+    <t>ARP.</t>
+  </si>
+  <si>
+    <t>RARP.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Le protocole </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ARP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Address Resolution Protocol) fait le lien entre la couche 3 (IP) et la couche 2 (MAC) en envoyant une requête de diffusion pour demander "qui possède cette IP ?".</t>
+    </r>
+  </si>
+  <si>
+    <t>Combien d'hôtes peut-on avoir avec un masque /30 ?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Un /30 offre 4 adresses au total ($2^2$). On soustrait l'adresse réseau et l'adresse de broadcast, il reste donc </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2 adresses utilisables</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (idéal pour les liaisons point à point).</t>
+    </r>
+  </si>
+  <si>
+    <t>Quel outil est utilisé pour analyser le trafic réseau ?</t>
+  </si>
+  <si>
+    <t>WireShark.</t>
+  </si>
+  <si>
+    <t>IPsec.</t>
+  </si>
+  <si>
+    <t>OpenVPN.</t>
+  </si>
+  <si>
+    <r>
+      <t>Wireshark</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> est un analyseur de protocoles (sniffer) qui permet de capturer et d'examiner chaque paquet circulant sur une interface réseau en temps réel.</t>
+    </r>
+  </si>
+  <si>
+    <t>Quelle commande Linux permet d'afficher les ports ouverts ?</t>
+  </si>
+  <si>
+    <t>Ip.</t>
+  </si>
+  <si>
+    <t>netstat.</t>
+  </si>
+  <si>
+    <t>open.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La commande </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>netstat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (souvent utilisée avec les options </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>-tulpn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) ou sa version moderne </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>ss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> permet de lister les sockets en écoute et les connexions actives.</t>
+    </r>
+  </si>
+  <si>
+    <t>Le protocole TCP est :</t>
+  </si>
+  <si>
+    <t>Rapide mais peu fiable.</t>
+  </si>
+  <si>
+    <t>Non connecté.</t>
+  </si>
+  <si>
+    <t>Orienté connexion.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Le </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>TCP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> est "orienté connexion" car il établit une session (Three-way handshake) avant l'échange de données, garantissant que les paquets arrivent dans le bon ordre et sans erreur.</t>
+    </r>
+  </si>
+  <si>
+    <t>Quelle est la longueur standard d'un masque de sous-réseau pour un réseau de classe C ?</t>
+  </si>
+  <si>
+    <t>/16</t>
+  </si>
+  <si>
+    <t>/24</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Historiquement, la </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Classe C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (plage 192.0.0.0 à 223.255.255.255) utilise par défaut un masque de 24 bits (255.255.255.0).</t>
+    </r>
+  </si>
+  <si>
+    <t>Combien d'hôtes peuvent être assignés dans un réseau /25 ?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Un /25 dispose de $2^7 = 128$ adresses. En retirant le réseau et le broadcast ($128 - 2$), on obtient </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>126 hôtes assignables</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Quel masque correspond à /26 ?</t>
+  </si>
+  <si>
+    <t>255.255.255.128</t>
+  </si>
+  <si>
+    <t>255.255.255.192</t>
+  </si>
+  <si>
+    <t>255.255.255.224</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Un masque /26 signifie que les 2 premiers bits du dernier octet sont à 1 ($128 + 64 = 192$). Le masque complet est donc </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>255.255.255.192</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Quelle est la plage d'adresses valides dans le sous-réseau 10.0.0.64/26 ?</t>
+  </si>
+  <si>
+    <t>10.0.0.64 - 10.0.0.127</t>
+  </si>
+  <si>
+    <t>10.0.0.65 - 10.0.0.126</t>
+  </si>
+  <si>
+    <t>10.0.0.66 - 10.0.0.126</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pour un /26, le bloc est de 64 adresses. Le réseau commence à .64 et finit à .127 (broadcast). Les adresses d'hôtes valides (utilisables) sont donc de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.65 à .126</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1071,6 +1854,12 @@
       <sz val="11"/>
       <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF444746"/>
+      <name val="Google Sans Text"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1109,7 +1898,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -1121,6 +1910,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -1424,15 +2216,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I50"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="23.6640625" customWidth="1"/>
     <col min="2" max="2" width="20.33203125" customWidth="1"/>
     <col min="9" max="9" width="46.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="55.8" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1461,7 +2253,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="97.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="97.2" thickBot="1">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1486,7 +2278,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="97.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="97.2" thickBot="1">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1511,7 +2303,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="124.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="124.8" thickBot="1">
       <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
@@ -1536,7 +2328,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="97.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="97.2" thickBot="1">
       <c r="A5" s="1" t="s">
         <v>24</v>
       </c>
@@ -1561,7 +2353,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="83.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="83.4" thickBot="1">
       <c r="A6" s="1" t="s">
         <v>29</v>
       </c>
@@ -1586,7 +2378,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="83.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="83.4" thickBot="1">
       <c r="A7" s="1" t="s">
         <v>34</v>
       </c>
@@ -1611,7 +2403,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="124.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="124.8" thickBot="1">
       <c r="A8" s="1" t="s">
         <v>39</v>
       </c>
@@ -1636,7 +2428,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="97.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" ht="97.2" thickBot="1">
       <c r="A9" s="1" t="s">
         <v>44</v>
       </c>
@@ -1661,7 +2453,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="83.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" ht="83.4" thickBot="1">
       <c r="A10" s="1" t="s">
         <v>49</v>
       </c>
@@ -1686,7 +2478,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="166.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" ht="166.2" thickBot="1">
       <c r="A11" s="1" t="s">
         <v>54</v>
       </c>
@@ -1711,7 +2503,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="97.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" ht="97.2" thickBot="1">
       <c r="A12" s="1" t="s">
         <v>59</v>
       </c>
@@ -1736,7 +2528,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="138.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="138.6" thickBot="1">
       <c r="A13" s="1" t="s">
         <v>64</v>
       </c>
@@ -1761,7 +2553,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="83.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" ht="83.4" thickBot="1">
       <c r="A14" s="1" t="s">
         <v>69</v>
       </c>
@@ -1786,7 +2578,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="83.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" ht="83.4" thickBot="1">
       <c r="A15" s="1" t="s">
         <v>74</v>
       </c>
@@ -1811,7 +2603,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="83.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" ht="83.4" thickBot="1">
       <c r="A16" s="1" t="s">
         <v>79</v>
       </c>
@@ -1836,7 +2628,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="83.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="83.4" thickBot="1">
       <c r="A17" s="1" t="s">
         <v>84</v>
       </c>
@@ -1861,7 +2653,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="83.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" ht="83.4" thickBot="1">
       <c r="A18" s="1" t="s">
         <v>87</v>
       </c>
@@ -1886,7 +2678,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="207.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" ht="207.6" thickBot="1">
       <c r="A19" s="1" t="s">
         <v>92</v>
       </c>
@@ -1911,7 +2703,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="83.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" ht="83.4" thickBot="1">
       <c r="A20" s="1" t="s">
         <v>97</v>
       </c>
@@ -1936,7 +2728,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="83.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" ht="83.4" thickBot="1">
       <c r="A21" s="1" t="s">
         <v>102</v>
       </c>
@@ -1961,7 +2753,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="166.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" ht="166.2" thickBot="1">
       <c r="A22" s="1" t="s">
         <v>107</v>
       </c>
@@ -1986,7 +2778,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="180" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" ht="180" thickBot="1">
       <c r="A23" s="1" t="s">
         <v>113</v>
       </c>
@@ -2011,7 +2803,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="83.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" ht="83.4" thickBot="1">
       <c r="A24" s="1" t="s">
         <v>118</v>
       </c>
@@ -2036,7 +2828,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="83.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" ht="83.4" thickBot="1">
       <c r="A25" s="1" t="s">
         <v>123</v>
       </c>
@@ -2061,7 +2853,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="124.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" ht="124.8" thickBot="1">
       <c r="A26" s="1" t="s">
         <v>128</v>
       </c>
@@ -2086,7 +2878,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="83.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" ht="83.4" thickBot="1">
       <c r="A27" s="1" t="s">
         <v>133</v>
       </c>
@@ -2111,7 +2903,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="83.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" ht="83.4" thickBot="1">
       <c r="A28" s="1" t="s">
         <v>138</v>
       </c>
@@ -2134,6 +2926,512 @@
       </c>
       <c r="I28" s="4" t="s">
         <v>142</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="83.4" thickBot="1">
+      <c r="A29" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="83.4" thickBot="1">
+      <c r="A30" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="83.4" thickBot="1">
+      <c r="A31" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H31" s="1">
+        <v>4</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="97.2" thickBot="1">
+      <c r="A32" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H32" s="1">
+        <v>3</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="83.4" thickBot="1">
+      <c r="A33" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33" s="1">
+        <v>1</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="83.4" thickBot="1">
+      <c r="A34" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H34" s="1">
+        <v>3</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="83.4" thickBot="1">
+      <c r="A35" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H35" s="1">
+        <v>2</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="83.4" thickBot="1">
+      <c r="A36" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H36" s="1">
+        <v>2</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="83.4" thickBot="1">
+      <c r="A37" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H37" s="1">
+        <v>1</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="83.4" thickBot="1">
+      <c r="A38" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H38" s="1">
+        <v>2</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="111" thickBot="1">
+      <c r="A39" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H39" s="1">
+        <v>3</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="83.4" thickBot="1">
+      <c r="A40" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H40" s="1">
+        <v>3</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="83.4" thickBot="1">
+      <c r="A41" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H41" s="1">
+        <v>1</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="83.4" thickBot="1">
+      <c r="A42" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H42" s="1">
+        <v>2</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="83.4" thickBot="1">
+      <c r="A43" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B43" s="3">
+        <v>2</v>
+      </c>
+      <c r="C43" s="3">
+        <v>4</v>
+      </c>
+      <c r="D43" s="3">
+        <v>6</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H43" s="1">
+        <v>1</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="83.4" thickBot="1">
+      <c r="A44" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H44" s="1">
+        <v>1</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="83.4" thickBot="1">
+      <c r="A45" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H45" s="1">
+        <v>2</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="83.4" thickBot="1">
+      <c r="A46" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H46" s="1">
+        <v>3</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="83.4" thickBot="1">
+      <c r="A47" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H47" s="1">
+        <v>2</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="83.4" thickBot="1">
+      <c r="A48" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B48" s="3">
+        <v>64</v>
+      </c>
+      <c r="C48" s="3">
+        <v>126</v>
+      </c>
+      <c r="D48" s="3">
+        <v>128</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H48" s="1">
+        <v>2</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="83.4" thickBot="1">
+      <c r="A49" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H49" s="1">
+        <v>2</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="83.4" thickBot="1">
+      <c r="A50" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H50" s="1">
+        <v>2</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -2145,7 +3443,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2154,7 +3452,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
